--- a/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-POMALCA.xlsx
+++ b/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-POMALCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-225128</t>
+          <t>I-225218</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-6.7708286</t>
+          <t>-6.7671846</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-79.7870572</t>
+          <t>-79.7804324</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Bolivia / Avenida Perú</t>
+          <t>Avenida José de San Martín / Calle José Carlos Mariátegui</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-225129</t>
+          <t>I-232628</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.7710067</t>
+          <t>-6.7700086</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-79.7870743</t>
+          <t>-79.7905414</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Bolivia / Avenida San Francisco de Asís</t>
+          <t>Calle Cuba / Calle México</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-225150</t>
+          <t>I-225087</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,22 +612,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.7705122</t>
+          <t>-6.7717749</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-79.7826145</t>
+          <t>-79.7752335</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida San Francisco de Asís / Calle Los Jazmines</t>
+          <t>Prolongación Avenida 9 de Octubre / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-232602</t>
+          <t>I-667254</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,22 +664,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-6.7702521</t>
+          <t>-6.764631</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-79.7821132</t>
+          <t>-79.7898254</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Perú / Calle Los Algarrobos</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-232603</t>
+          <t>I-579104</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-6.7704572</t>
+          <t>-6.7644457</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-79.782154</t>
+          <t>-79.7915469</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida San Francisco de Asís / Calle Los Algarrobos</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-232650</t>
+          <t>I-579105</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,285 +768,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.7700987</t>
+          <t>-6.7650079</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-79.778826</t>
+          <t>-79.7917539</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida San Francisco de Asís</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>l-232856</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>-6.7703979</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-79.7816582</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Avenida San Francisco de Asís / Calle Misericordia</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>l-232878</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-6.7703867</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-79.7830318</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Avenida Perú</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>l-232879</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-6.7705638</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-79.7830552</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Avenida San Francisco de Asís</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>l-232941</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-6.7699818</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-79.7790817</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Avenida Perú / Jr. Leoncio Prado</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>l-232943</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-6.7701287</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-79.7791027</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Avenida San Francisco de Asís / Jr. Leoncio Prado</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
         <is>
           <t>140118</t>
         </is>

--- a/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-POMALCA.xlsx
+++ b/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-POMALCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida José de San Martín / Calle José Carlos Mariátegui</t>
+          <t>Avenida José de San Martín / Calle 20 de Enero / Calle José Carlos Mariátegui / Prolongación Avenida José de San Martín</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -778,15 +778,327 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>Calle Héroes del Cenepa / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>140118</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>I-225088</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-6.7661997</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-79.7863264</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Avenida Bolivia / Calle Estados Unidos / Prolongación Avenida José de San Martín</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>140118</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I-667257</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-6.7647245</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-79.7886956</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>140118</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-579092</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-6.7656325</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-79.7899515</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Calle Cuba / Calle Estados Unidos</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>140118</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-579093</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-6.7656964</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-79.7888678</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Calle Estados Unidos / Calle Santo Domingo</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>140118</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-660627</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-6.7761108</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-79.7766118</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>140118</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-667223</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-6.766082</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-79.793401</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>140118</t>
         </is>

--- a/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-POMALCA.xlsx
+++ b/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-POMALCA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-225218</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-6.7671846</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>140118</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-232628</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-6.7700086</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>140118</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-225087</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-6.7717749</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>140118</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-667254</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-6.764631</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>140118</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-579104</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-6.7644457</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>140118</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-579105</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-6.7650079</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>140118</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-225088</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-6.7661997</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>140118</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-667257</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-6.7647245</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>140118</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-579092</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-6.7656325</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>140118</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-579093</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-6.7656964</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>140118</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-660627</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-6.7761108</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>140118</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-667223</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-6.766082</t>
@@ -1096,11 +1036,6 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>140118</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-POMALCA.xlsx
+++ b/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-POMALCA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-POMALCA.xlsx
+++ b/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-POMALCA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-POMALCA.xlsx
+++ b/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-POMALCA.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-225218</t>
+          <t>I-667257</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-6.7671846</t>
+          <t>-6.7647245</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-79.7804324</t>
+          <t>-79.7886956</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida José de San Martín / Calle 20 de Enero / Calle José Carlos Mariátegui / Prolongación Avenida José de San Martín</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,22 +533,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-232628</t>
+          <t>I-667254</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.7700086</t>
+          <t>-6.764631</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-79.7905414</t>
+          <t>-79.7898254</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Calle Cuba / Calle México</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-225087</t>
+          <t>I-667223</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.7717749</t>
+          <t>-6.766082</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-79.7752335</t>
+          <t>-79.793401</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Prolongación Avenida 9 de Octubre / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,17 +627,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-667254</t>
+          <t>I-660627</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-6.764631</t>
+          <t>-6.7761108</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-79.7898254</t>
+          <t>-79.7766118</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -674,17 +674,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-579104</t>
+          <t>I-579105</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-6.7644457</t>
+          <t>-6.7650079</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-79.7915469</t>
+          <t>-79.7917539</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-579105</t>
+          <t>I-579104</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.7650079</t>
+          <t>-6.7644457</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-79.7917539</t>
+          <t>-79.7915469</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Calle Héroes del Cenepa / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-225088</t>
+          <t>I-579093</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.7661997</t>
+          <t>-6.7656964</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-79.7863264</t>
+          <t>-79.7888678</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Bolivia / Calle Estados Unidos / Prolongación Avenida José de San Martín</t>
+          <t>Calle Estados Unidos / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-667257</t>
+          <t>I-579092</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-6.7647245</t>
+          <t>-6.7656325</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-79.7886956</t>
+          <t>-79.7899515</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Estados Unidos / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -862,22 +862,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-579092</t>
+          <t>I-232628</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.7656325</t>
+          <t>-6.7700086</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-79.7899515</t>
+          <t>-79.7905414</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Calle Cuba / Calle Estados Unidos</t>
+          <t>Calle Cuba / Calle México</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -909,22 +909,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-579093</t>
+          <t>I-225218</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-6.7656964</t>
+          <t>-6.7671846</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-79.7888678</t>
+          <t>-79.7804324</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Calle Estados Unidos / Calle Santo Domingo</t>
+          <t>Avenida José de San Martín / Calle José Carlos Mariátegui</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-660627</t>
+          <t>I-225088</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-6.7761108</t>
+          <t>-6.7661997</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-79.7766118</t>
+          <t>-79.7863264</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Bolivia / Calle Estados Unidos / Prolongación Avenida José de San Martín</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-667223</t>
+          <t>I-225087</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-6.766082</t>
+          <t>-6.7717749</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-79.793401</t>
+          <t>-79.7752335</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Prolongación Avenida 9 de Octubre / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
